--- a/jira_export_2026-07-16.xlsx
+++ b/jira_export_2026-07-16.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>327 h</t>
+          <t>335 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>497.16</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>68.56999999999999</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>399.3</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>99.83</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="34">
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>1189.5</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>1189.5</v>
+        <v>951.6</v>
       </c>
     </row>
     <row r="35">
@@ -3475,9 +3475,9 @@
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="16" t="n">
@@ -4182,7 +4182,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>1252.2</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>834.8</v>
+        <v>715.54</v>
       </c>
     </row>
     <row r="49">
@@ -4326,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>1028.4</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>411.36</v>
+        <v>373.96</v>
       </c>
     </row>
     <row r="51">
@@ -7503,27 +7503,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7543,29 +7543,29 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O95" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7575,32 +7575,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7610,34 +7610,34 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="O96" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7647,12 +7647,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
@@ -7698,16 +7698,16 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O97" s="17" t="n">
         <v>0</v>
@@ -7719,12 +7719,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7759,27 +7759,27 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>255</v>
+        <v>1000</v>
       </c>
       <c r="O98" s="17" t="n">
         <v>0</v>
@@ -7791,12 +7791,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
@@ -7842,16 +7842,16 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="O99" s="17" t="n">
         <v>0</v>
@@ -7863,27 +7863,27 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
@@ -7914,16 +7914,16 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -7935,32 +7935,32 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7970,34 +7970,34 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="O101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -8007,12 +8007,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
@@ -8058,18 +8058,18 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O102" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8079,27 +8079,27 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -8119,29 +8119,29 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.75</v>
+        <v>6.25</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8151,32 +8151,32 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8186,28 +8186,28 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>6.25</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
@@ -8223,32 +8223,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8258,28 +8258,28 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
@@ -8342,16 +8342,16 @@
         <v>6</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8414,16 +8414,16 @@
         <v>6</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8439,32 +8439,32 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de Calais</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
@@ -8474,28 +8474,28 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8511,32 +8511,30 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v/>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -8546,34 +8544,34 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O109" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8583,30 +8581,32 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8616,34 +8616,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
@@ -8716,41 +8716,39 @@
         <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8760,12 +8758,12 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
@@ -8776,33 +8774,33 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="16" t="n">
-        <v>405</v>
+        <v>2812.32</v>
+      </c>
+      <c r="O112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8812,11 +8810,13 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8835,27 +8835,27 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.5</v>
+        <v>1.15</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>2812.32</v>
+        <v>392.5</v>
       </c>
       <c r="O113" s="17" t="n">
         <v>0</v>
@@ -8918,16 +8918,16 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>392.5</v>
+        <v>1556.25</v>
       </c>
       <c r="O114" s="17" t="n">
         <v>0</v>
@@ -8990,16 +8990,16 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>1556.25</v>
+        <v>1790</v>
       </c>
       <c r="O115" s="17" t="n">
         <v>0</v>
@@ -9062,18 +9062,18 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9155,12 +9155,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9170,13 +9170,11 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v/>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9190,28 +9188,28 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>1.15</v>
+        <v>4.25</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9227,12 +9225,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9242,7 +9240,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9260,34 +9258,34 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O119" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="13" t="n">
@@ -9297,12 +9295,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9312,52 +9310,38 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F120" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F120" s="15" t="inlineStr"/>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr"/>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27557</t>
-        </is>
-      </c>
-      <c r="M120" s="15" t="inlineStr">
-        <is>
-          <t>00144532</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr"/>
+      <c r="M120" s="15" t="inlineStr"/>
       <c r="N120" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9367,12 +9351,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9382,67 +9366,83 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="inlineStr"/>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L121" s="12" t="inlineStr"/>
-      <c r="M121" s="12" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L121" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-26814</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>00142941</t>
+        </is>
+      </c>
       <c r="N121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O121" s="13" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P121" s="13" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
@@ -9456,65 +9456,63 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1.25</v>
+        <v>9.25</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O122" s="16" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v/>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
@@ -9533,29 +9531,29 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>9.25</v>
+        <v>1.5</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O123" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9565,12 +9563,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9580,7 +9578,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9598,34 +9596,34 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9635,22 +9633,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9673,23 +9671,23 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9705,12 +9703,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9720,7 +9718,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9738,28 +9736,28 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9824,12 +9822,12 @@
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9845,22 +9843,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9883,29 +9881,29 @@
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O128" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9915,22 +9913,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9938,7 +9936,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -9948,32 +9946,32 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>2323</v>
+        <v>964.1</v>
       </c>
       <c r="O129" s="17" t="n">
         <v>0</v>
@@ -9985,12 +9983,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -10034,19 +10032,19 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>964.1</v>
+        <v>140.4</v>
       </c>
       <c r="O130" s="17" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="P130" s="16" t="n">
         <v>0</v>
@@ -10055,22 +10053,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10078,7 +10076,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -10088,35 +10086,35 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="O131" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
+      </c>
+      <c r="O131" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
         <v>0</v>
@@ -10125,22 +10123,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10158,28 +10156,28 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10195,22 +10193,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10228,28 +10226,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>2</v>
+        <v>0.19</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10310,16 +10308,16 @@
         <v>12</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10350,7 +10348,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10380,16 +10378,16 @@
         <v>12</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10420,7 +10418,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10450,16 +10448,16 @@
         <v>12</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10475,12 +10473,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10490,7 +10488,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10508,28 +10506,28 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10545,22 +10543,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10583,23 +10581,23 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K138" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10615,22 +10613,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10638,7 +10636,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10653,29 +10651,29 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="13" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O139" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="13" t="n">
@@ -10685,22 +10683,18 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr"/>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10708,7 +10702,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10734,19 +10728,19 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O140" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O140" s="16" t="n">
+        <v>575</v>
       </c>
       <c r="P140" s="16" t="n">
         <v>0</v>
@@ -10755,18 +10749,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="inlineStr"/>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10784,35 +10782,35 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="13" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10821,22 +10819,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10854,34 +10852,34 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O142" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
@@ -10891,22 +10889,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10929,27 +10927,27 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="O143" s="17" t="n">
         <v>0</v>
@@ -10961,22 +10959,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10992,36 +10990,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H144" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H144" s="15" t="inlineStr"/>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M144" s="15" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr"/>
+      <c r="M144" s="15" t="inlineStr"/>
       <c r="N144" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
@@ -11031,22 +11017,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11062,10 +11048,14 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
@@ -11074,8 +11064,16 @@
       <c r="K145" s="12" t="n">
         <v>1.25</v>
       </c>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11089,12 +11087,12 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
@@ -11104,7 +11102,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11122,28 +11120,28 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11159,12 +11157,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11174,7 +11172,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11192,28 +11190,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11229,12 +11227,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11244,7 +11242,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11267,23 +11265,23 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11299,22 +11297,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11327,35 +11325,27 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L149" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27535</t>
-        </is>
-      </c>
-      <c r="M149" s="12" t="inlineStr">
-        <is>
-          <t>465345</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L149" s="12" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr"/>
       <c r="N149" s="13" t="n">
         <v>0</v>
       </c>
@@ -11369,22 +11359,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11402,7 +11392,7 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
@@ -11414,7 +11404,7 @@
         <v>19</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
+        <v>4.5</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11431,22 +11421,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11454,7 +11444,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -11476,7 +11466,7 @@
         <v>19</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11493,12 +11483,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11508,7 +11498,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11521,31 +11511,39 @@
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L152" s="15" t="inlineStr"/>
-      <c r="M152" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M152" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O152" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="16" t="n">
@@ -11555,22 +11553,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11578,7 +11576,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -11588,34 +11586,34 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11640,7 +11638,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11674,7 +11672,7 @@
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
@@ -11695,22 +11693,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11718,40 +11716,32 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M155" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>4.25</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr"/>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
@@ -11765,22 +11755,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11788,7 +11778,7 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
@@ -11798,19 +11788,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>4.25</v>
+        <v>0.25</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11827,22 +11817,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11855,7 +11845,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -11865,17 +11855,25 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L157" s="12" t="inlineStr"/>
-      <c r="M157" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L157" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N157" s="13" t="n">
         <v>0</v>
       </c>
@@ -11889,12 +11887,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11904,7 +11902,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11917,7 +11915,7 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
@@ -11927,25 +11925,17 @@
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M158" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr"/>
+      <c r="M158" s="15" t="inlineStr"/>
       <c r="N158" s="16" t="n">
         <v>0</v>
       </c>
@@ -11959,22 +11949,22 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11997,14 +11987,14 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -12021,22 +12011,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12059,14 +12049,14 @@
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>29</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L160" s="15" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -12083,22 +12073,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12116,19 +12106,19 @@
       </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1</v>
+        <v>7.25</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12145,22 +12135,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12173,27 +12163,35 @@
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="L162" s="15" t="inlineStr"/>
-      <c r="M162" s="15" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M162" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N162" s="16" t="n">
         <v>0</v>
       </c>
@@ -12207,22 +12205,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12238,32 +12236,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H163" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H163" s="12" t="inlineStr"/>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L163" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M163" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr"/>
+      <c r="M163" s="12" t="inlineStr"/>
       <c r="N163" s="13" t="n">
         <v>0</v>
       </c>
@@ -12277,12 +12263,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12292,7 +12278,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12305,22 +12291,30 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H164" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M164" s="15" t="inlineStr"/>
       <c r="N164" s="16" t="n">
         <v>0</v>
@@ -12335,12 +12329,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -12350,7 +12344,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD79 - Deux Sèvres</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12373,20 +12367,16 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L165" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
       <c r="N165" s="13" t="n">
         <v>0</v>
@@ -12401,26 +12391,28 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
-        </is>
-      </c>
-      <c r="E166" s="15" t="n">
-        <v/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E166" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
@@ -12446,7 +12438,7 @@
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12463,12 +12455,12 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
@@ -12478,12 +12470,12 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>Déploiement de Littéralis Expert</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
@@ -12498,7 +12490,7 @@
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I167" s="12" t="inlineStr">
@@ -12510,7 +12502,7 @@
         <v>34</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>0.5</v>
+        <v>8.75</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12527,27 +12519,23 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C168" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr"/>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E168" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
@@ -12562,19 +12550,19 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>8.75</v>
+        <v>1.75</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12591,25 +12579,21 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr"/>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr"/>
       <c r="F169" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12617,31 +12601,35 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H169" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr"/>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr"/>
-      <c r="M169" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N169" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O169" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O169" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P169" s="13" t="n">
@@ -12651,18 +12639,18 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr"/>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E170" s="15" t="inlineStr"/>
@@ -12679,27 +12667,27 @@
       <c r="H170" s="15" t="inlineStr"/>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K170" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-32829</t>
         </is>
       </c>
       <c r="M170" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00163534</t>
         </is>
       </c>
       <c r="N170" s="16" t="n">
-        <v>510.6</v>
+        <v>50</v>
       </c>
       <c r="O170" s="17" t="n">
         <v>0</v>
@@ -12711,18 +12699,18 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr"/>
@@ -12733,35 +12721,27 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr"/>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M171" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr"/>
       <c r="N171" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O171" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P171" s="13" t="n">
@@ -12771,18 +12751,18 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr"/>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr"/>
@@ -12799,14 +12779,14 @@
       <c r="H172" s="15" t="inlineStr"/>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12943,13 +12923,13 @@
       <c r="L175" s="18" t="inlineStr"/>
       <c r="M175" s="18" t="inlineStr"/>
       <c r="N175" s="19" t="n">
-        <v>70876.86</v>
+        <v>69305.66</v>
       </c>
       <c r="O175" s="19" t="n">
         <v>26599.77</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>133.01</v>
+        <v>129.45</v>
       </c>
     </row>
   </sheetData>
@@ -13136,18 +13116,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
@@ -13162,7 +13142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 0 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 1 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13224,8 +13204,83 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33755</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MAINTENON</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33762</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>00169559</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr"/>
+      <c r="C6" s="18" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="inlineStr"/>
+      <c r="G6" s="18" t="inlineStr"/>
+      <c r="H6" s="18" t="inlineStr"/>
+      <c r="I6" s="18" t="inlineStr"/>
+      <c r="J6" s="18" t="inlineStr"/>
+      <c r="K6" s="19" t="n">
+        <v>815</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13699,16 +13754,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>106</v>
+        <v>110.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>30.75</v>
+        <v>31</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>139.5</v>
+        <v>144.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>36</v>
@@ -13718,7 +13773,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13784,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>52.5</v>
+        <v>53.25</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5.75</v>
@@ -13738,17 +13793,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>58.75</v>
+        <v>59.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -13760,7 +13815,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>74.33</v>
+        <v>75.08</v>
       </c>
     </row>
   </sheetData>
@@ -13924,7 +13979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13948,7 +14003,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 8 commande(s)</t>
+          <t>Épics créées ce mois — 9 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14003,34 +14058,34 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34566</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34559</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
+          <t>COMMUNE DE RIEZ</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Services</t>
@@ -14038,7 +14093,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00154892</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -14048,22 +14103,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -14073,7 +14128,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -14083,32 +14138,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14128,32 +14183,32 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14163,7 +14218,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -14173,22 +14228,22 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -14198,7 +14253,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14218,32 +14273,32 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>4475</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -14263,32 +14318,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>2035</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -14298,7 +14353,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -14308,83 +14363,107 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I13" s="26" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>8 commande(s)</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>13610</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
@@ -14395,17 +14474,17 @@
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>9 commande(s)</t>
         </is>
       </c>
       <c r="I14" s="25" t="n">
-        <v>4300</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B15" s="18" t="n"/>
@@ -14416,10 +14495,31 @@
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="18" t="inlineStr">
         <is>
-          <t>7 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="n">
         <v>9310</v>
       </c>
     </row>

--- a/jira_export_2026-07-16.xlsx
+++ b/jira_export_2026-07-16.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>335 h</t>
+          <t>349 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>7</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>8</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>15</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>19</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11932,7 +11932,7 @@
         <v>28</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L158" s="15" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -12180,7 +12180,7 @@
         <v>34</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L162" s="15" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>26599.77</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>129.45</v>
+        <v>123.15</v>
       </c>
     </row>
   </sheetData>
@@ -13116,16 +13116,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -13142,7 +13142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 1 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 2 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -13207,22 +13207,22 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H5" s="12" t="n">
@@ -13245,12 +13245,12 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33762</t>
+          <t>PDMDEP-34343</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>00169559</t>
+          <t>00171709</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
@@ -13258,28 +13258,82 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33755</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MAINTENON</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33762</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>00169559</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="19" t="n">
-        <v>815</v>
+      <c r="B7" s="18" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr"/>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
+      <c r="F7" s="18" t="inlineStr"/>
+      <c r="G7" s="18" t="inlineStr"/>
+      <c r="H7" s="18" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr"/>
+      <c r="J7" s="18" t="inlineStr"/>
+      <c r="K7" s="19" t="n">
+        <v>1630</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13754,26 +13808,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>110.25</v>
+        <v>114</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>31</v>
+        <v>31.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>144.25</v>
+        <v>148.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -13784,7 +13838,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>53.25</v>
+        <v>59.25</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5.75</v>
@@ -13793,7 +13847,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>59.5</v>
+        <v>65.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15</v>
@@ -13803,7 +13857,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13869,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>75.08</v>
+        <v>75.83</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-16.xlsx
+++ b/jira_export_2026-07-16.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>26,600 €</t>
+          <t>30,037 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,14 +769,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>6,017 €</t>
+          <t>8,455 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>20,583 €</t>
+          <t>21,582 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>349 h</t>
+          <t>354 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -1621,11 +1621,11 @@
       <c r="N12" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="O12" s="17" t="n">
-        <v>0</v>
+      <c r="O12" s="16" t="n">
+        <v>450</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
         <v>1296</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>1872</v>
+        <v>1944</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>249.6</v>
+        <v>228.71</v>
       </c>
     </row>
     <row r="17">
@@ -2254,10 +2254,10 @@
         <v>848.7</v>
       </c>
       <c r="O21" s="17" t="n">
-        <v>0</v>
+        <v>141.45</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>141.45</v>
       </c>
     </row>
     <row r="22">
@@ -2830,10 +2830,10 @@
         <v>2100</v>
       </c>
       <c r="O29" s="17" t="n">
-        <v>1400</v>
+        <v>1505</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>430.77</v>
+        <v>463.08</v>
       </c>
     </row>
     <row r="30">
@@ -3118,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>399.3</v>
+        <v>532.4</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>76.06</v>
+        <v>101.41</v>
       </c>
     </row>
     <row r="34">
@@ -4270,10 +4270,10 @@
         <v>0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="50">
@@ -5398,7 +5398,7 @@
         <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
@@ -5413,11 +5413,11 @@
       <c r="N65" s="13" t="n">
         <v>705</v>
       </c>
-      <c r="O65" s="17" t="n">
-        <v>0</v>
+      <c r="O65" s="13" t="n">
+        <v>1057.5</v>
       </c>
       <c r="P65" s="13" t="n">
-        <v>0</v>
+        <v>528.75</v>
       </c>
     </row>
     <row r="66">
@@ -5485,8 +5485,8 @@
       <c r="N66" s="16" t="n">
         <v>564</v>
       </c>
-      <c r="O66" s="17" t="n">
-        <v>0</v>
+      <c r="O66" s="16" t="n">
+        <v>705</v>
       </c>
       <c r="P66" s="16" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
@@ -5845,11 +5845,11 @@
       <c r="N71" s="13" t="n">
         <v>142.1</v>
       </c>
-      <c r="O71" s="17" t="n">
-        <v>0</v>
+      <c r="O71" s="13" t="n">
+        <v>142.1</v>
       </c>
       <c r="P71" s="13" t="n">
-        <v>0</v>
+        <v>189.47</v>
       </c>
     </row>
     <row r="72">
@@ -7566,10 +7566,10 @@
         <v>0</v>
       </c>
       <c r="O95" s="13" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="96">
@@ -8786,10 +8786,10 @@
         <v>2812.32</v>
       </c>
       <c r="O112" s="17" t="n">
-        <v>0</v>
+        <v>300.28</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0</v>
+        <v>200.19</v>
       </c>
     </row>
     <row r="113">
@@ -12180,7 +12180,7 @@
         <v>34</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="L162" s="15" t="inlineStr">
         <is>
@@ -12926,10 +12926,10 @@
         <v>69305.66</v>
       </c>
       <c r="O175" s="19" t="n">
-        <v>26599.77</v>
+        <v>30037.3</v>
       </c>
       <c r="P175" s="19" t="n">
-        <v>123.15</v>
+        <v>136.85</v>
       </c>
     </row>
   </sheetData>
@@ -13808,7 +13808,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>114</v>
+        <v>117.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>31.75</v>
@@ -13817,7 +13817,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>148.75</v>
+        <v>152.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>39</v>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>75.83</v>
+        <v>77.33</v>
       </c>
     </row>
   </sheetData>
@@ -13954,16 +13954,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>397233</v>
+        <v>393796</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>205338</v>
+        <v>203691</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>191895</v>
+        <v>190105</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>154589</v>
+        <v>152799</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -13979,16 +13979,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>186393</v>
+        <v>183955</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>80046</v>
+        <v>79398</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106347</v>
+        <v>104557</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>92049</v>
+        <v>90259</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>
@@ -14004,10 +14004,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>210840</v>
+        <v>209840</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>125292</v>
+        <v>124292</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>85548</v>
